--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,34 +796,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123873899</v>
+        <v>135077155</v>
       </c>
       <c r="B3" t="n">
-        <v>58790</v>
+        <v>56833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -866,22 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,52 +904,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103079905</v>
+        <v>123873899</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>58790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerum, Enerum, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619653</v>
+        <v>619655</v>
       </c>
       <c r="R4" t="n">
-        <v>6353426</v>
+        <v>6353694</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,19 +972,24 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,29 +998,26 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Olof Einarsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Olof Einarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103079906</v>
+        <v>103079905</v>
       </c>
       <c r="B5" t="n">
         <v>106813</v>
@@ -1058,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619707</v>
+        <v>619653</v>
       </c>
       <c r="R5" t="n">
-        <v>6353508</v>
+        <v>6353426</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1086,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
+          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1129,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103079907</v>
+        <v>103079906</v>
       </c>
       <c r="B6" t="n">
         <v>106813</v>
@@ -1168,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619649</v>
+        <v>619707</v>
       </c>
       <c r="R6" t="n">
-        <v>6353533</v>
+        <v>6353508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,17 +1196,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
+          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103079908</v>
+        <v>103079907</v>
       </c>
       <c r="B7" t="n">
         <v>106813</v>
@@ -1278,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619619</v>
+        <v>619649</v>
       </c>
       <c r="R7" t="n">
-        <v>6353564</v>
+        <v>6353533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1306,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
+          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1349,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103079909</v>
+        <v>103079908</v>
       </c>
       <c r="B8" t="n">
         <v>106813</v>
@@ -1388,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619688</v>
+        <v>619619</v>
       </c>
       <c r="R8" t="n">
-        <v>6353553</v>
+        <v>6353564</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1416,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
+          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1459,7 +1457,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103079921</v>
+        <v>103079909</v>
       </c>
       <c r="B9" t="n">
         <v>106813</v>
@@ -1498,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619624</v>
+        <v>619688</v>
       </c>
       <c r="R9" t="n">
-        <v>6353626</v>
+        <v>6353553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,17 +1526,17 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
+          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103081016</v>
+        <v>103079921</v>
       </c>
       <c r="B10" t="n">
         <v>106813</v>
@@ -1608,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619738</v>
+        <v>619624</v>
       </c>
       <c r="R10" t="n">
-        <v>6353522</v>
+        <v>6353626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,17 +1636,17 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
+          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1666,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1679,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103081026</v>
+        <v>103081016</v>
       </c>
       <c r="B11" t="n">
         <v>106813</v>
@@ -1718,10 +1716,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619639</v>
+        <v>619738</v>
       </c>
       <c r="R11" t="n">
-        <v>6353675</v>
+        <v>6353522</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,17 +1746,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
+          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,7 +1787,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103178444</v>
+        <v>103081026</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1828,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619676</v>
+        <v>619639</v>
       </c>
       <c r="R12" t="n">
-        <v>6353448</v>
+        <v>6353675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,17 +1856,17 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
+          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1888,7 +1886,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1899,7 +1897,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103178445</v>
+        <v>103178444</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -1938,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619687</v>
+        <v>619676</v>
       </c>
       <c r="R13" t="n">
-        <v>6353463</v>
+        <v>6353448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,7 +1966,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
+          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2009,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103178446</v>
+        <v>103178445</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2048,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619706</v>
+        <v>619687</v>
       </c>
       <c r="R14" t="n">
-        <v>6353481</v>
+        <v>6353463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +2076,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2119,7 +2117,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103178452</v>
+        <v>103178446</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2158,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619614</v>
+        <v>619706</v>
       </c>
       <c r="R15" t="n">
-        <v>6353646</v>
+        <v>6353481</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,17 +2186,17 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
+          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,7 +2227,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103178453</v>
+        <v>103178452</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2268,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619658</v>
+        <v>619614</v>
       </c>
       <c r="R16" t="n">
-        <v>6353642</v>
+        <v>6353646</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2296,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
+          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2339,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103178454</v>
+        <v>103178453</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2378,10 +2376,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619633</v>
+        <v>619658</v>
       </c>
       <c r="R17" t="n">
-        <v>6353676</v>
+        <v>6353642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,7 +2406,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2442,6 +2440,116 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103178454</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>619633</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6353676</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134089639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135077155</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123873899</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079905</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079907</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079908</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079909</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103079921</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081016</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178444</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2114,6 +2179,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178445</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2224,6 +2294,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178446</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2334,6 +2409,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178452</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2444,6 +2524,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178453</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2554,8 +2639,32 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178454</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>135077155</v>
       </c>
       <c r="B3" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,34 +806,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123873899</v>
+        <v>135077155</v>
       </c>
       <c r="B3" t="n">
-        <v>58790</v>
+        <v>56838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -876,22 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +896,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -918,58 +913,59 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123873899</t>
+          <t>https://artportalen.se/Sighting/135077155</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103079905</v>
+        <v>123873899</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>58790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalmar län, Öl</t>
+          <t>Enerum, Enerum, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619653</v>
+        <v>619655</v>
       </c>
       <c r="R4" t="n">
-        <v>6353426</v>
+        <v>6353694</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,19 +987,24 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,34 +1013,31 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Olof Einarsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Olof Einarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079905</t>
+          <t>https://artportalen.se/Sighting/123873899</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103079906</v>
+        <v>103079905</v>
       </c>
       <c r="B5" t="n">
         <v>106813</v>
@@ -1078,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619707</v>
+        <v>619653</v>
       </c>
       <c r="R5" t="n">
-        <v>6353508</v>
+        <v>6353426</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1106,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
+          <t>ED182FE4-AFCE-402A-A37E-2992B8066C93</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1148,13 +1146,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079906</t>
+          <t>https://artportalen.se/Sighting/103079905</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103079907</v>
+        <v>103079906</v>
       </c>
       <c r="B6" t="n">
         <v>106813</v>
@@ -1193,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619649</v>
+        <v>619707</v>
       </c>
       <c r="R6" t="n">
-        <v>6353533</v>
+        <v>6353508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,17 +1221,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
+          <t>2AC7F7E6-5CBD-466B-92C0-0E6E3DED1700</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,13 +1261,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079907</t>
+          <t>https://artportalen.se/Sighting/103079906</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103079908</v>
+        <v>103079907</v>
       </c>
       <c r="B7" t="n">
         <v>106813</v>
@@ -1308,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619619</v>
+        <v>619649</v>
       </c>
       <c r="R7" t="n">
-        <v>6353564</v>
+        <v>6353533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1336,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
+          <t>D4900CAF-BD07-4EFC-9330-5517E673C015</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1378,13 +1376,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079908</t>
+          <t>https://artportalen.se/Sighting/103079907</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103079909</v>
+        <v>103079908</v>
       </c>
       <c r="B8" t="n">
         <v>106813</v>
@@ -1423,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619688</v>
+        <v>619619</v>
       </c>
       <c r="R8" t="n">
-        <v>6353553</v>
+        <v>6353564</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1451,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
+          <t>12835BE1-3C75-4565-9968-03573BA3FA7F</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1493,13 +1491,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079909</t>
+          <t>https://artportalen.se/Sighting/103079908</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103079921</v>
+        <v>103079909</v>
       </c>
       <c r="B9" t="n">
         <v>106813</v>
@@ -1538,10 +1536,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619624</v>
+        <v>619688</v>
       </c>
       <c r="R9" t="n">
-        <v>6353626</v>
+        <v>6353553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,17 +1566,17 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
+          <t>EC18F362-DCF8-4E86-9E2E-935E98013859</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,13 +1606,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103079921</t>
+          <t>https://artportalen.se/Sighting/103079909</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103081016</v>
+        <v>103079921</v>
       </c>
       <c r="B10" t="n">
         <v>106813</v>
@@ -1653,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619738</v>
+        <v>619624</v>
       </c>
       <c r="R10" t="n">
-        <v>6353522</v>
+        <v>6353626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,17 +1681,17 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
+          <t>79039EE4-060C-4FFB-BC7D-70301702AABF</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1711,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Emma Svensson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1723,13 +1721,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081016</t>
+          <t>https://artportalen.se/Sighting/103079921</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103081026</v>
+        <v>103081016</v>
       </c>
       <c r="B11" t="n">
         <v>106813</v>
@@ -1768,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619639</v>
+        <v>619738</v>
       </c>
       <c r="R11" t="n">
-        <v>6353675</v>
+        <v>6353522</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,17 +1796,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
+          <t>ABB7898B-444A-463A-A4D7-0336B97DFB10</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,13 +1836,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103081026</t>
+          <t>https://artportalen.se/Sighting/103081016</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103178444</v>
+        <v>103081026</v>
       </c>
       <c r="B12" t="n">
         <v>106813</v>
@@ -1883,10 +1881,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619676</v>
+        <v>619639</v>
       </c>
       <c r="R12" t="n">
-        <v>6353448</v>
+        <v>6353675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,17 +1911,17 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
+          <t>560D793C-2074-4028-BFE4-8EFFA33CBBC9</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,7 +1941,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+          <t>Thomas Johansson, Emma Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1953,13 +1951,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178444</t>
+          <t>https://artportalen.se/Sighting/103081026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103178445</v>
+        <v>103178444</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -1998,10 +1996,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619687</v>
+        <v>619676</v>
       </c>
       <c r="R13" t="n">
-        <v>6353463</v>
+        <v>6353448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2026,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
+          <t>59387962-4D8F-4C7E-A329-AA81ECEC4D0F</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2068,13 +2066,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178445</t>
+          <t>https://artportalen.se/Sighting/103178444</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103178446</v>
+        <v>103178445</v>
       </c>
       <c r="B14" t="n">
         <v>106813</v>
@@ -2113,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619706</v>
+        <v>619687</v>
       </c>
       <c r="R14" t="n">
-        <v>6353481</v>
+        <v>6353463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2141,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
+          <t>56DD9BEC-CC2C-4262-B4A9-452E257C2EF6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2183,13 +2181,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178446</t>
+          <t>https://artportalen.se/Sighting/103178445</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103178452</v>
+        <v>103178446</v>
       </c>
       <c r="B15" t="n">
         <v>106813</v>
@@ -2228,10 +2226,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619614</v>
+        <v>619706</v>
       </c>
       <c r="R15" t="n">
-        <v>6353646</v>
+        <v>6353481</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,17 +2256,17 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
+          <t>042842D6-6121-4937-9035-CEC2FF6C5E40</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,13 +2296,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178452</t>
+          <t>https://artportalen.se/Sighting/103178446</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103178453</v>
+        <v>103178452</v>
       </c>
       <c r="B16" t="n">
         <v>106813</v>
@@ -2343,10 +2341,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619658</v>
+        <v>619614</v>
       </c>
       <c r="R16" t="n">
-        <v>6353642</v>
+        <v>6353646</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,7 +2371,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
+          <t>4A1421DA-9CC6-48E5-B0F1-3D5CD870256A</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2413,13 +2411,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103178453</t>
+          <t>https://artportalen.se/Sighting/103178452</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103178454</v>
+        <v>103178453</v>
       </c>
       <c r="B17" t="n">
         <v>106813</v>
@@ -2458,10 +2456,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619633</v>
+        <v>619658</v>
       </c>
       <c r="R17" t="n">
-        <v>6353676</v>
+        <v>6353642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2486,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+          <t>7272A729-AB1A-470E-9B46-021CB2561611</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2527,6 +2525,121 @@
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178453</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103178454</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalmar län, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>619633</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6353676</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>11817AF3-C94E-4270-A165-B823BE8ACC08</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-10-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103178454</t>
         </is>
@@ -2550,6 +2663,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2740-2022 artfynd.xlsx
+++ b/artfynd/S 2740-2022 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>135077155</v>
       </c>
       <c r="B3" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
